--- a/offers/seasonal/عروض انوجين.xlsx
+++ b/offers/seasonal/عروض انوجين.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -92,6 +92,12 @@
   </si>
   <si>
     <t>INNOGEN RESTORE 10ML 30VIAL </t>
+  </si>
+  <si>
+    <t>نوع العرض</t>
+  </si>
+  <si>
+    <t>كمية</t>
   </si>
 </sst>
 </file>
@@ -516,7 +522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G245"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="46.625" style="2" customWidth="1"/>
@@ -527,7 +533,7 @@
     <col min="7" max="7" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -546,9 +552,11 @@
       <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G1" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="8">
         <v>43316</v>
       </c>
@@ -567,8 +575,11 @@
       <c r="F2" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="8">
         <v>44972</v>
       </c>
@@ -587,8 +598,11 @@
       <c r="F3" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="8">
         <v>26292</v>
       </c>
@@ -607,8 +621,11 @@
       <c r="F4" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="8">
         <v>44962</v>
       </c>
@@ -627,8 +644,11 @@
       <c r="F5" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="8">
         <v>26293</v>
       </c>
@@ -647,8 +667,11 @@
       <c r="F6" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="8">
         <v>43303</v>
       </c>
@@ -667,8 +690,11 @@
       <c r="F7" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="8">
         <v>43314</v>
       </c>
@@ -687,8 +713,11 @@
       <c r="F8" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="8">
         <v>43318</v>
       </c>
@@ -696,7 +725,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="3">
-        <v>75.900000000000006</v>
+        <v>75.9</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>6</v>
@@ -707,8 +736,11 @@
       <c r="F9" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="8">
         <v>43315</v>
       </c>
@@ -727,8 +759,11 @@
       <c r="F10" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="8">
         <v>44967</v>
       </c>
@@ -747,8 +782,11 @@
       <c r="F11" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="8">
         <v>44963</v>
       </c>
@@ -767,8 +805,11 @@
       <c r="F12" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="8">
         <v>26291</v>
       </c>
@@ -787,8 +828,11 @@
       <c r="F13" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="8">
         <v>43304</v>
       </c>
@@ -807,8 +851,11 @@
       <c r="F14" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="8">
         <v>43317</v>
       </c>
@@ -827,8 +874,11 @@
       <c r="F15" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G15" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="8">
         <v>44965</v>
       </c>
@@ -847,8 +897,11 @@
       <c r="F16" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="8">
         <v>44964</v>
       </c>
@@ -867,8 +920,11 @@
       <c r="F17" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="8">
         <v>44966</v>
       </c>
@@ -887,821 +943,824 @@
       <c r="F18" s="5">
         <v>46275</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
     </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
     </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
     </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
     </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
     </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
     </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
     </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
     </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
     </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
     </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
     </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
     </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
     </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
     </row>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
     </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
     </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
     </row>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
     </row>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
     </row>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
     </row>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
     </row>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
     </row>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
     </row>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
     </row>
-    <row r="96" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
     </row>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
     </row>
-    <row r="99" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
     </row>
-    <row r="102" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="102">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="103">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
     </row>
-    <row r="104" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="104">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="105">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
     </row>
-    <row r="106" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="106">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
     </row>
-    <row r="107" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="107">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
     </row>
-    <row r="108" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="108">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="109">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="110">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
     </row>
-    <row r="111" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="111">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="112">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
     </row>
-    <row r="113" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="113">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
     </row>
-    <row r="114" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="114">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
     </row>
-    <row r="115" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="115">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
     </row>
-    <row r="116" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="116">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
     </row>
-    <row r="117" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="117">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
     </row>
-    <row r="118" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="118">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
     </row>
-    <row r="119" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="119">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
     </row>
-    <row r="120" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="120">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
     </row>
-    <row r="121" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="121">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
     </row>
-    <row r="122" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="122">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
     </row>
-    <row r="123" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="123">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
     </row>
-    <row r="124" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="124">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
     </row>
-    <row r="125" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="125">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
     </row>
-    <row r="126" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="126">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
     </row>
-    <row r="127" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="127">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
     </row>
-    <row r="128" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="128">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
     </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="129">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
     </row>
-    <row r="130" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="130">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
     </row>
-    <row r="131" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="131">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
     </row>
-    <row r="132" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="132">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
     </row>
-    <row r="133" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="133">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
     </row>
-    <row r="134" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="134">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
     </row>
-    <row r="135" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="135">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="136">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
     </row>
-    <row r="137" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="137">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
     </row>
-    <row r="138" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="138">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
     </row>
-    <row r="139" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="139">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
     </row>
-    <row r="140" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="140">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
     </row>
-    <row r="141" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="141">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
     </row>
-    <row r="142" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="142">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
     </row>
-    <row r="143" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="143">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
     </row>
-    <row r="144" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="144">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="145">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
     </row>
-    <row r="146" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="146">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="147">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
     </row>
-    <row r="148" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="148">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="149">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="150">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
     </row>
-    <row r="151" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="151">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
     </row>
-    <row r="152" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="152">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
     </row>
-    <row r="153" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="153">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
     </row>
-    <row r="154" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="154">
       <c r="D154" s="3"/>
     </row>
-    <row r="155" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="155">
       <c r="D155" s="3"/>
     </row>
-    <row r="156" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="156">
       <c r="D156" s="3"/>
     </row>
-    <row r="157" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="157">
       <c r="D157" s="3"/>
     </row>
-    <row r="158" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="158">
       <c r="D158" s="3"/>
     </row>
-    <row r="159" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="159">
       <c r="D159" s="3"/>
     </row>
-    <row r="160" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="160">
       <c r="D160" s="3"/>
     </row>
-    <row r="161" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="161">
       <c r="D161" s="3"/>
     </row>
-    <row r="162" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="162">
       <c r="D162" s="3"/>
     </row>
-    <row r="163" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="163">
       <c r="D163" s="3"/>
     </row>
-    <row r="164" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="164">
       <c r="D164" s="3"/>
     </row>
-    <row r="165" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="165">
       <c r="D165" s="3"/>
     </row>
-    <row r="166" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="166">
       <c r="D166" s="3"/>
     </row>
-    <row r="167" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="167">
       <c r="D167" s="3"/>
     </row>
-    <row r="168" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="168">
       <c r="D168" s="3"/>
     </row>
-    <row r="169" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="169">
       <c r="D169" s="3"/>
     </row>
-    <row r="170" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="170">
       <c r="D170" s="3"/>
     </row>
-    <row r="171" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="171">
       <c r="D171" s="3"/>
     </row>
-    <row r="172" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="172">
       <c r="D172" s="3"/>
     </row>
-    <row r="173" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="173">
       <c r="D173" s="3"/>
     </row>
-    <row r="174" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="174">
       <c r="D174" s="3"/>
     </row>
-    <row r="175" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="175">
       <c r="D175" s="3"/>
     </row>
-    <row r="176" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="176">
       <c r="D176" s="3"/>
     </row>
-    <row r="177" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="177">
       <c r="D177" s="3"/>
     </row>
-    <row r="178" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="178">
       <c r="D178" s="3"/>
     </row>
-    <row r="179" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="179">
       <c r="D179" s="3"/>
     </row>
-    <row r="180" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="180">
       <c r="D180" s="3"/>
     </row>
-    <row r="181" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="181">
       <c r="D181" s="3"/>
     </row>
-    <row r="182" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="182">
       <c r="D182" s="3"/>
     </row>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="183">
       <c r="D183" s="3"/>
     </row>
-    <row r="184" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="184">
       <c r="D184" s="3"/>
     </row>
-    <row r="185" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="185">
       <c r="D185" s="3"/>
     </row>
-    <row r="186" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="186">
       <c r="D186" s="3"/>
     </row>
-    <row r="187" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="187">
       <c r="D187" s="3"/>
     </row>
-    <row r="188" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="188">
       <c r="D188" s="3"/>
     </row>
-    <row r="189" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="189">
       <c r="D189" s="3"/>
     </row>
-    <row r="190" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="190">
       <c r="D190" s="3"/>
     </row>
-    <row r="191" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="191">
       <c r="D191" s="3"/>
     </row>
-    <row r="192" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="192">
       <c r="D192" s="3"/>
     </row>
-    <row r="193" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="193">
       <c r="D193" s="3"/>
     </row>
-    <row r="194" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="194">
       <c r="D194" s="3"/>
     </row>
-    <row r="195" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="195">
       <c r="D195" s="3"/>
     </row>
-    <row r="196" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="196">
       <c r="D196" s="3"/>
     </row>
-    <row r="197" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="197">
       <c r="D197" s="3"/>
     </row>
-    <row r="198" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="198">
       <c r="D198" s="3"/>
     </row>
-    <row r="199" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="199">
       <c r="D199" s="3"/>
     </row>
-    <row r="200" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="200">
       <c r="D200" s="3"/>
     </row>
-    <row r="201" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="201">
       <c r="D201" s="3"/>
     </row>
-    <row r="202" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="202">
       <c r="D202" s="3"/>
     </row>
-    <row r="203" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="203">
       <c r="D203" s="3"/>
     </row>
-    <row r="204" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="204">
       <c r="D204" s="3"/>
     </row>
-    <row r="205" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="205">
       <c r="D205" s="3"/>
     </row>
-    <row r="206" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="206">
       <c r="D206" s="3"/>
     </row>
-    <row r="207" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="207">
       <c r="D207" s="3"/>
     </row>
-    <row r="208" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="208">
       <c r="D208" s="3"/>
     </row>
-    <row r="209" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="209">
       <c r="D209" s="3"/>
     </row>
-    <row r="210" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="210">
       <c r="D210" s="3"/>
     </row>
-    <row r="211" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="211">
       <c r="D211" s="3"/>
     </row>
-    <row r="212" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="212">
       <c r="D212" s="3"/>
     </row>
-    <row r="213" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="213">
       <c r="D213" s="3"/>
     </row>
-    <row r="214" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="214">
       <c r="D214" s="3"/>
     </row>
-    <row r="215" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="215">
       <c r="D215" s="3"/>
     </row>
-    <row r="216" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="216">
       <c r="D216" s="3"/>
     </row>
-    <row r="217" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="217">
       <c r="D217" s="3"/>
     </row>
-    <row r="218" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="218">
       <c r="D218" s="3"/>
     </row>
-    <row r="219" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="219">
       <c r="D219" s="3"/>
     </row>
-    <row r="220" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="220">
       <c r="D220" s="3"/>
     </row>
-    <row r="221" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="221">
       <c r="D221" s="3"/>
     </row>
-    <row r="222" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="222">
       <c r="D222" s="3"/>
     </row>
-    <row r="223" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="223">
       <c r="D223" s="3"/>
     </row>
-    <row r="224" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="224">
       <c r="D224" s="3"/>
     </row>
-    <row r="225" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="225">
       <c r="D225" s="3"/>
     </row>
-    <row r="226" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="226">
       <c r="D226" s="3"/>
     </row>
-    <row r="227" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="227">
       <c r="D227" s="3"/>
     </row>
-    <row r="228" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="228">
       <c r="D228" s="3"/>
     </row>
-    <row r="229" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="229">
       <c r="D229" s="3"/>
     </row>
-    <row r="230" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="230">
       <c r="D230" s="3"/>
     </row>
-    <row r="231" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="231">
       <c r="D231" s="3"/>
     </row>
-    <row r="232" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="232">
       <c r="D232" s="3"/>
     </row>
-    <row r="233" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="233">
       <c r="D233" s="3"/>
     </row>
-    <row r="234" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="234">
       <c r="D234" s="3"/>
     </row>
-    <row r="235" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="235">
       <c r="D235" s="3"/>
     </row>
-    <row r="236" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="236">
       <c r="D236" s="3"/>
     </row>
-    <row r="237" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="237">
       <c r="D237" s="3"/>
     </row>
-    <row r="238" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="238">
       <c r="D238" s="3"/>
     </row>
-    <row r="239" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="239">
       <c r="D239" s="3"/>
     </row>
-    <row r="240" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="240">
       <c r="D240" s="3"/>
     </row>
-    <row r="241" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="241">
       <c r="D241" s="3"/>
     </row>
-    <row r="242" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="242">
       <c r="D242" s="3"/>
     </row>
-    <row r="243" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="243">
       <c r="D243" s="3"/>
     </row>
-    <row r="244" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="244">
       <c r="D244" s="3"/>
     </row>
-    <row r="245" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="245">
       <c r="D245" s="3"/>
     </row>
   </sheetData>
